--- a/data_out/country_spreadsheets/Latvia.xlsx
+++ b/data_out/country_spreadsheets/Latvia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>29.87</v>
       </c>
+      <c r="X2" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>167.1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>211.25</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>111.04</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>122.47</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>102.12</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>29.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>24.82</v>
       </c>
+      <c r="X3" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>124.39</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>117.82</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>44.56</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>24.82</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>13.1</v>
       </c>
+      <c r="X4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>104.21</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>175.34</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>207.57</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>113.64</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>17.82</v>
       </c>
+      <c r="X5" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>58</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>203.86</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>133.92</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>104.36</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>17.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>6.96</v>
       </c>
+      <c r="X6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>173.86</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>108.68</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6.96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1004,6 +1344,57 @@
         <v>54.28</v>
       </c>
       <c r="W7" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22.87</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>197.04</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>236.49</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>108.84</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AN7" t="n">
         <v>49.73</v>
       </c>
     </row>
